--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_173_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_173_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6543</v>
+        <v>5.5385</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7267</v>
+        <v>6.1068</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0724</v>
+        <v>-0.5683</v>
       </c>
       <c r="G2" t="n">
         <v>2.8548</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2865</v>
+        <v>1.1707</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2729</v>
+        <v>0.653</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0136</v>
+        <v>0.5177</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1107</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9552</v>
+        <v>4.3063</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0153</v>
+        <v>2.7361</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9399</v>
+        <v>1.5702</v>
       </c>
       <c r="G3" t="n">
         <v>0.9805</v>
@@ -688,13 +688,13 @@
         <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5108</v>
+        <v>0.8619</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6256</v>
+        <v>0.3464</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8852</v>
+        <v>0.5155</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3806</v>
+        <v>1.7255</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3072</v>
+        <v>1.8537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07340000000000001</v>
+        <v>-0.1282</v>
       </c>
       <c r="G4" t="n">
         <v>2.0031</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8698</v>
+        <v>-0.525</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2617</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3919</v>
+        <v>0.1902</v>
       </c>
       <c r="V4" t="n">
         <v>-1.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4319</v>
+        <v>1.5952</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2358</v>
+        <v>0.095</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6676</v>
+        <v>1.5003</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4735</v>
+        <v>-2.5844</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06850000000000001</v>
+        <v>1.6383</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.542</v>
+        <v>-4.2228</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1376</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1008</v>
+        <v>2.1146</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>-3.1121</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6112</v>
+        <v>-1.5869</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0323</v>
+        <v>-0.4762</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5788</v>
+        <v>-1.1107</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>3.0154</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>3.0154</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0224</v>
+        <v>0.2339</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3734</v>
+        <v>-0.1215</v>
       </c>
       <c r="U5" t="n">
-        <v>0.351</v>
+        <v>0.3554</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2842</v>
+        <v>0.5162</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.88</v>
+        <v>-0.1178</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1642</v>
+        <v>0.634</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.5844</v>
+        <v>-0.4735</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6383</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.2228</v>
+        <v>-0.542</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.1376</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1146</v>
+        <v>0.1008</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.1121</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5869</v>
+        <v>-0.6112</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4762</v>
+        <v>-0.0323</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1107</v>
+        <v>-0.5788</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0154</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.0154</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0772</v>
+        <v>0.0619</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0965</v>
+        <v>-0.2555</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0193</v>
+        <v>0.3174</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1508</v>
+        <v>0.0508</v>
       </c>
       <c r="E7" t="n">
         <v>0.4624</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6132</v>
+        <v>-0.4116</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8756</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0253</v>
+        <v>-0.8237</v>
       </c>
       <c r="T7" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6519</v>
+        <v>-0.4503</v>
       </c>
       <c r="V7" t="n">
         <v>1.7501</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9307</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8682</v>
+        <v>0.4393</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0625</v>
+        <v>-1.2302</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2503</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0073</v>
+        <v>0.0517</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2576</v>
+        <v>-0.9101</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1214</v>
+        <v>0.1208</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2318</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.129</v>
+        <v>-0.9792</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2391</v>
+        <v>-0.0323</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.368</v>
+        <v>-0.9469</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1573</v>
+        <v>-0.0226</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4129</v>
+        <v>0.3185</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2557</v>
+        <v>-0.3411</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0604</v>
+        <v>-1.4025</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2034</v>
+        <v>-1.34</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2638</v>
+        <v>-0.0625</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.2503</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0517</v>
+        <v>0.0073</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9101</v>
+        <v>-0.2576</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1208</v>
+        <v>-0.1214</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.2318</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9792</v>
+        <v>-0.129</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0323</v>
+        <v>0.2391</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9469</v>
+        <v>-0.368</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2921</v>
+        <v>-0.3145</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0589</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3747</v>
+        <v>-0.2557</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8158</v>
+        <v>-1.556</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0378</v>
+        <v>0.1548</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.778</v>
+        <v>-1.7108</v>
       </c>
       <c r="G10" t="n">
         <v>1.3792</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8909</v>
+        <v>-0.6311</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>-0.3301</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3681</v>
+        <v>-0.3009</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5519</v>
+        <v>-2.1653</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1265</v>
+        <v>-3.2694</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5746</v>
+        <v>1.1041</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7401</v>
@@ -1312,13 +1312,13 @@
         <v>3.0154</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1186</v>
+        <v>0.5052</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1712</v>
+        <v>-0.3141</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2898</v>
+        <v>0.8193</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4665</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9312</v>
+        <v>-5.8058</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5859</v>
+        <v>-3.3933</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3452</v>
+        <v>-2.4124</v>
       </c>
       <c r="G12" t="n">
         <v>0.6062</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6818</v>
+        <v>-0.5564</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>-0.2475</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2416</v>
+        <v>-0.3088</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1444</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.265400000000002</v>
+        <v>2.0121</v>
       </c>
       <c r="E13" t="n">
-        <v>2.980800000000001</v>
+        <v>3.7276</v>
       </c>
       <c r="F13" t="n">
         <v>-1.7154</v>
       </c>
       <c r="G13" t="n">
-        <v>2.041500000000001</v>
+        <v>2.0415</v>
       </c>
       <c r="H13" t="n">
         <v>9.921299999999999</v>
@@ -1468,13 +1468,13 @@
         <v>17.3966</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7863000000000002</v>
+        <v>-0.03970000000000018</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8452</v>
+        <v>-1.0983</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0588</v>
+        <v>1.0587</v>
       </c>
       <c r="V13" t="n">
         <v>-3.4691</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.539999999999999</v>
+        <v>10.4164</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4619</v>
+        <v>7.9337</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0781</v>
+        <v>2.4827</v>
       </c>
       <c r="G14" t="n">
         <v>6.7939</v>
@@ -1546,13 +1546,13 @@
         <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3673</v>
+        <v>0.5091</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6915</v>
+        <v>-0.2197</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3242</v>
+        <v>0.7288</v>
       </c>
       <c r="V14" t="n">
         <v>2.6495</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0348</v>
+        <v>3.6256</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4919</v>
+        <v>1.7053</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4571</v>
+        <v>1.9203</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8824</v>
+        <v>0.9395</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1018</v>
+        <v>0.15</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9842</v>
+        <v>0.7895</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4732</v>
+        <v>0.7579</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1176</v>
+        <v>1.1196</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3555</v>
+        <v>-0.3616</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5908</v>
+        <v>0.1815</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2195</v>
+        <v>-0.9696</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3713</v>
+        <v>1.1511</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5461</v>
+        <v>0.168</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5895</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0435</v>
+        <v>0.8832</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0026</v>
+        <v>2.2862</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6083</v>
+        <v>2.8223</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8729</v>
+        <v>3.2536</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2335</v>
+        <v>3.6099</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6394</v>
+        <v>-0.3563</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9395</v>
+        <v>0.8824</v>
       </c>
       <c r="H16" t="n">
-        <v>0.15</v>
+        <v>-1.1018</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7895</v>
+        <v>1.9842</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7579</v>
+        <v>2.4732</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1196</v>
+        <v>0.1176</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3616</v>
+        <v>2.3555</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1815</v>
+        <v>-1.5908</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9696</v>
+        <v>-1.2195</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1511</v>
+        <v>-0.3713</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5847</v>
+        <v>-0.3273</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.187</v>
+        <v>-0.4716</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.1443</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2862</v>
+        <v>2.0026</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8223</v>
+        <v>1.6083</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.945</v>
+        <v>0.541</v>
       </c>
       <c r="E17" t="n">
-        <v>3.321</v>
+        <v>1.6696</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3759</v>
+        <v>-1.1286</v>
       </c>
       <c r="G17" t="n">
         <v>-0.74</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6876</v>
+        <v>1.2836</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0331</v>
+        <v>0.3817</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6546</v>
+        <v>0.9019</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9304</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0438</v>
+        <v>0.1338</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3662</v>
+        <v>1.4225</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3224</v>
+        <v>-1.2888</v>
       </c>
       <c r="G18" t="n">
         <v>0.4383</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2138</v>
+        <v>0.3038</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5059</v>
+        <v>0.5623</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2403</v>
+        <v>-2.748</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0565</v>
+        <v>-4.4225</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1838</v>
+        <v>1.6745</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3273</v>
+        <v>0.1297</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6481</v>
+        <v>-1.8378</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6792</v>
+        <v>1.9675</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1776</v>
+        <v>0.3877</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0672</v>
+        <v>-0.9005</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1104</v>
+        <v>1.2882</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5049</v>
+        <v>-0.258</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7153</v>
+        <v>-0.9373</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7896</v>
+        <v>0.6793</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5909</v>
+        <v>0.282</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2161</v>
+        <v>-0.5423</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3747</v>
+        <v>0.8244</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3828</v>
+        <v>-2.8135</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7764</v>
+        <v>-0.8206</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3936</v>
+        <v>-1.9929</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1297</v>
+        <v>-1.3273</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8378</v>
+        <v>-0.6481</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9675</v>
+        <v>-0.6792</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3877</v>
+        <v>0.1776</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9005</v>
+        <v>0.0672</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2882</v>
+        <v>0.1104</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.258</v>
+        <v>-1.5049</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9373</v>
+        <v>-0.7153</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6793</v>
+        <v>-0.7896</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0876</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3528</v>
+        <v>-0.1641</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8962</v>
+        <v>0.0198</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5434</v>
+        <v>-0.1838</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7886</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9939</v>
+        <v>-3.1625</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0416</v>
+        <v>-1.3339</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9523</v>
+        <v>-1.8286</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1004</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.1878</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6563</v>
+        <v>0.0514</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0127</v>
+        <v>0.1364</v>
       </c>
       <c r="V21" t="n">
         <v>0.6778999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1298</v>
+        <v>-3.9161</v>
       </c>
       <c r="E22" t="n">
         <v>-3.3812</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7486</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2045</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0901</v>
+        <v>0.3038</v>
       </c>
       <c r="T22" t="n">
         <v>0.1968</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1067</v>
+        <v>0.107</v>
       </c>
       <c r="V22" t="n">
         <v>0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.955</v>
+        <v>-4.2365</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9033</v>
+        <v>-4.6674</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0517</v>
+        <v>0.4309</v>
       </c>
       <c r="G23" t="n">
         <v>-3.853</v>
@@ -2248,13 +2248,13 @@
         <v>2.5515</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1199</v>
+        <v>0.5985</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5579</v>
+        <v>-0.322</v>
       </c>
       <c r="U23" t="n">
-        <v>0.438</v>
+        <v>0.9206</v>
       </c>
       <c r="V23" t="n">
         <v>-1.214</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.265300000000003</v>
+        <v>1.093800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7155</v>
+        <v>1.7154</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9807</v>
+        <v>-0.6216000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0414</v>
@@ -2326,13 +2326,13 @@
         <v>13.9172</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7862</v>
+        <v>3.1452</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0587</v>
+        <v>-1.0588</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8452</v>
+        <v>4.2043</v>
       </c>
       <c r="V24" t="n">
         <v>3.469200000000001</v>
